--- a/results/meta_analysis_ready/meta_analysis_ready_datasets.xlsx
+++ b/results/meta_analysis_ready/meta_analysis_ready_datasets.xlsx
@@ -7,21 +7,22 @@
   </bookViews>
   <sheets>
     <sheet name="Finalization_Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Meta_Analysis_Manifest" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="All_Approved_Outcomes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="primary_rct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="secondary_observational" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sensitivity_rct" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Meta_Analysis_Guidance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Base_Group_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Meta_Analysis_Manifest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All_Approved_Outcomes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="primary_rct" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="secondary_observational" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sensitivity_rct" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Meta_Analysis_Guidance" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'sensitivity_rct'!$A$1:$BM$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'sensitivity_rct'!$A$1:$BX$5</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="247">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -35,7 +36,7 @@
     <t xml:space="preserve">Efficacy and safety of preoperative or perioperative SGLT2 inhibitors in adult cardiac surgery: a systematic review and meta-analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Human-approved rows</t>
+    <t xml:space="preserve">Human-approved outcome rows</t>
   </si>
   <si>
     <t xml:space="preserve">6</t>
@@ -44,12 +45,18 @@
     <t xml:space="preserve">Human-approved studies</t>
   </si>
   <si>
-    <t xml:space="preserve">Analysis groups</t>
+    <t xml:space="preserve">Final analysis sets</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
+    <t xml:space="preserve">Sanitized non-applicable cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
     <t xml:space="preserve">Selection rule</t>
   </si>
   <si>
@@ -74,18 +81,69 @@
     <t xml:space="preserve">meta_analysis_role</t>
   </si>
   <si>
+    <t xml:space="preserve">role_class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">study_design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base_study_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary_RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postoperative acute kidney injury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary_Observational</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observational secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observational</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity_RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensitivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis_set_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_composite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parent_analysis_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_analysis_groups</t>
+  </si>
+  <si>
     <t xml:space="preserve">study_count</t>
   </si>
   <si>
     <t xml:space="preserve">outcome_row_count</t>
   </si>
   <si>
-    <t xml:space="preserve">study_design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outcome</t>
-  </si>
-  <si>
     <t xml:space="preserve">timepoint</t>
   </si>
   <si>
@@ -110,13 +168,10 @@
     <t xml:space="preserve">dataset_file</t>
   </si>
   <si>
-    <t xml:space="preserve">Primary_RCT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary RCT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Postoperative acute kidney injury</t>
+    <t xml:space="preserve">standalone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
   </si>
   <si>
     <t xml:space="preserve">Within 7 postoperative days; First 7 days postoperatively; Perioperative period (up to ~120 h postoperatively)</t>
@@ -125,24 +180,21 @@
     <t xml:space="preserve">Mixed</t>
   </si>
   <si>
-    <t xml:space="preserve">Random-effects by default; justify fixed-effect if used</t>
+    <t xml:space="preserve">RR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random-effects by default; final choice belongs to the analysis stage</t>
   </si>
   <si>
     <t xml:space="preserve">NO unless explicitly prespecified and methodologically justified</t>
   </si>
   <si>
-    <t xml:space="preserve">Do not pool yet: effect measures are mixed. Harmonize or analyze separately.</t>
+    <t xml:space="preserve">Proceed to R/27 after confirming clinical compatibility.</t>
   </si>
   <si>
     <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_primary_rct.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">Secondary_Observational</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observational secondary</t>
-  </si>
-  <si>
     <t xml:space="preserve">Within 7 days after surgery; Within 7 days post-op</t>
   </si>
   <si>
@@ -152,330 +204,378 @@
     <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_secondary_observational.csv</t>
   </si>
   <si>
-    <t xml:space="preserve">Sensitivity_RCT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitivity RCT</t>
+    <t xml:space="preserve">Primary RCT; Sensitivity RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">composite_sensitivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary_RCT + Sensitivity_RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within 7 postoperative days; First 7 days postoperatively; Perioperative period (up to ~120 h postoperatively); Within 7 days after surgery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_sensitivity_rct.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">screening_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outcome_row_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outcome_priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outcome_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">outcome_definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intervention_events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intervention_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comparator_events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comparator_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intervention_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intervention_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intervention_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comparator_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comparator_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comparator_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">effect_estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lower_ci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upper_ci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjustment_variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extraction_notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verification_tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verification_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_include_in_planned_analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_outcome_definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_timepoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_data_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_intervention_events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_intervention_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_comparator_events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_comparator_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_effect_measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_effect_estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_lower_ci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_upper_ci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_adjustment_variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_verified_source_location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human_outcome_notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verified_at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_outcome_definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_timepoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_data_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_intervention_events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_intervention_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_comparator_events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_comparator_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_effect_measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_effect_estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_lower_ci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_upper_ci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_adjusted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_adjustment_variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_source_location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_intervention_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_intervention_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_intervention_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_comparator_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_comparator_sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_comparator_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">final_study_design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">design_class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">effect_measure_source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input_validation_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input_validation_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000083_OUT_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KDIGO-defined AKI within 7 days after surgery: increase in serum creatinine ≥0.3 mg/dL within 48 h, or ≥1.5× baseline within 7 days, or urine output &lt;0.5 mL/kg/h for 6–12 h.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within 7 postoperative days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dichotomous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 2; Results section (Primary Outcome)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKI occurred in 111/392 (28%) in the dapagliflozin group and 205/392 (52%) in the placebo group during the first 7 postoperative days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent-extracted analysis-critical outcome data accepted without correction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1st Author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13 21:58:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multicenter, randomized, double-blind, placebo-controlled superiority trial (RCT).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default_RR_for_raw_dichotomous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw_dichotomous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000024_OUT_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKI within the first 7 days after cardiac surgery according to KDIGO 2012 criteria (serum creatinine and urine output).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First 7 days postoperatively</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Results section 3.2 Kidney injury; Figure 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKI occurred in 5/25 (20%) in the empagliflozin group vs 20/30 (66.7%) in control; absolute difference 46.7% (95% CI −69.7 to −23.6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prospective, single-center, open-label, phase IV, randomized, parallel-group controlled pilot trial (1:1). Intention-to-treat analysis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000098_OUT_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incidence of perioperative acute kidney injury defined by KDIGO criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perioperative period (up to ~120 h postoperatively)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Results section; Figure 1E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKI incidence 40.7% in dapagliflozin vs 41.0% in control; RR 0.99; 95% CI 0.69–1.44; P = .977.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raw event counts not reported; percentages and RR provided.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Randomized, open-label, blinded-endpoint trial (mITT analysis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verified_explicit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCR_000012_OUT_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKI within 7 days after CABG, meeting ≥1 stage 1 criterion from KDIGO, AKIN, or RIFLE definitions (adjudicated)</t>
   </si>
   <si>
     <t xml:space="preserve">Within 7 days after surgery</t>
   </si>
   <si>
-    <t xml:space="preserve">dichotomous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw_dichotomous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proceed to analysis-specific meta-analysis after checking clinical and methodological compatibility.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:/Users/Jason/Projects/srma-agent-toolkit/data/processed/meta_analysis_ready/meta_analysis_ready_sensitivity_rct.csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">screening_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outcome_row_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outcome_priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outcome_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">outcome_definition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intervention_events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intervention_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparator_events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparator_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intervention_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intervention_sd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intervention_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparator_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparator_sd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparator_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">effect_estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lower_ci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upper_ci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adjustment_variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source_location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">source_evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extraction_notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verification_tier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verification_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_include_in_planned_analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_outcome_definition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_timepoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_data_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_intervention_events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_intervention_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_comparator_events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_comparator_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_effect_measure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_effect_estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_lower_ci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_upper_ci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_adjustment_variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_verified_source_location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">human_outcome_notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verified_at</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_outcome_definition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_timepoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_data_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_intervention_events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_intervention_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_comparator_events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_comparator_total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_effect_measure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_effect_estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_lower_ci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_upper_ci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_adjusted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_adjustment_variables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_source_location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final_design_for_manifest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCR_000083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCR_000083_OUT_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KDIGO-defined AKI within 7 days after surgery: increase in serum creatinine ≥0.3 mg/dL within 48 h, or ≥1.5× baseline within 7 days, or urine output &lt;0.5 mL/kg/h for 6–12 h.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Within 7 postoperative days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 2; Results section (Primary Outcome)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKI occurred in 111/392 (28%) in the dapagliflozin group and 205/392 (52%) in the placebo group during the first 7 postoperative days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent-extracted analysis-critical outcome data accepted without correction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1st Author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13 21:58:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCR_000024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCR_000024_OUT_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKI within the first 7 days after cardiac surgery according to KDIGO 2012 criteria (serum creatinine and urine output).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First 7 days postoperatively</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Results section 3.2 Kidney injury; Figure 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKI occurred in 5/25 (20%) in the empagliflozin group vs 20/30 (66.7%) in control; absolute difference 46.7% (95% CI −69.7 to −23.6).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCR_000098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCR_000098_OUT_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incidence of perioperative acute kidney injury defined by KDIGO criteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perioperative period (up to ~120 h postoperatively)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risk ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Results section; Figure 1E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKI incidence 40.7% in dapagliflozin vs 41.0% in control; RR 0.99; 95% CI 0.69–1.44; P = .977.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raw event counts not reported; percentages and RR provided.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCR_000012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCR_000012_OUT_001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKI within 7 days after CABG, meeting ≥1 stage 1 criterion from KDIGO, AKIN, or RIFLE definitions (adjudicated)</t>
-  </si>
-  <si>
     <t xml:space="preserve">16</t>
   </si>
   <si>
@@ -497,6 +597,9 @@
     <t xml:space="preserve">Tier 2</t>
   </si>
   <si>
+    <t xml:space="preserve">Single-center, investigator-initiated, pragmatic, randomized, open-label trial with blinded outcome adjudication (modified intention-to-treat analysis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SCR_000096</t>
   </si>
   <si>
@@ -533,6 +636,9 @@
     <t xml:space="preserve">Tier 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Single-centre retrospective cohort with overlap-weighted propensity score causal analysis</t>
+  </si>
+  <si>
     <t xml:space="preserve">SCR_000118</t>
   </si>
   <si>
@@ -563,43 +669,70 @@
     <t xml:space="preserve">Weighted marginal risk ratio 0.63 (95% CI 0.44–0.91; p=0.014) favoring SGLT2i.</t>
   </si>
   <si>
-    <t xml:space="preserve">UNIVERSAL META-ANALYSIS GUIDANCE</t>
+    <t xml:space="preserve">Single-center retrospective cohort with causal inference weighting (entropy balancing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL META-ANALYSIS READY GUIDANCE</t>
   </si>
   <si>
     <t xml:space="preserve">--------------------------------------------------</t>
   </si>
   <si>
-    <t xml:space="preserve">Human-approved analysis groups: 3</t>
+    <t xml:space="preserve">Human-approved studies: 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final analysis sets: 3</t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">Selection rule:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  human_include_in_planned_analysis == Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  AND verification_status == Verified / Corrected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analysis-set rule:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Sensitivity sets include the compatible parent primary set plus sensitivity-only rows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downstream rule:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Analyze each final analysis set separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Do not combine different evidence designs or effect measures without explicit methodological justification.</t>
+  </si>
+  <si>
     <t xml:space="preserve">[1] Primary_RCT</t>
   </si>
   <si>
     <t xml:space="preserve">  Role: Primary RCT</t>
   </si>
   <si>
+    <t xml:space="preserve">  Set type: standalone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Source group(s): Primary_RCT</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Studies: 3</t>
   </si>
   <si>
-    <t xml:space="preserve">  Outcome: Postoperative acute kidney injury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Design: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Effect measure: Mixed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Input type: Mixed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Suggested model: Random-effects by default; justify fixed-effect if used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Recommendation: Do not pool yet: effect measures are mixed. Harmonize or analyze separately.</t>
+    <t xml:space="preserve">  Design: RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Effect measure: RR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Next: Proceed to R/27 after confirming clinical compatibility.</t>
   </si>
   <si>
     <t xml:space="preserve">[2] Secondary_Observational</t>
@@ -608,49 +741,28 @@
     <t xml:space="preserve">  Role: Observational secondary</t>
   </si>
   <si>
+    <t xml:space="preserve">  Source group(s): Secondary_Observational</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Studies: 2</t>
   </si>
   <si>
-    <t xml:space="preserve">  Input type: reported_effect</t>
+    <t xml:space="preserve">  Design: Observational</t>
   </si>
   <si>
     <t xml:space="preserve">[3] Sensitivity_RCT</t>
   </si>
   <si>
-    <t xml:space="preserve">  Role: Sensitivity RCT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Studies: 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Effect measure: 64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Input type: raw_dichotomous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Recommendation: Proceed to analysis-specific meta-analysis after checking clinical and methodological compatibility.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GENERAL RULES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Analyze each analysis_group separately unless a combined analysis was explicitly prespecified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Do not combine materially different study designs into one pooled estimate by default.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Do not silently combine RR, OR, HR, MD, SMD, or other incompatible effect measures.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Prefer adjusted effect estimates for observational studies when the planned estimand requires them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Use sensitivity analyses to test robustness when broader eligibility or alternative definitions are allowed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Interpret the primary analysis according to its prespecified evidence role; treat complementary analyses as supportive unless otherwise defined.</t>
+    <t xml:space="preserve">  Role: Primary RCT; Sensitivity RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Set type: composite_sensitivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Source group(s): Primary_RCT + Sensitivity_RCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Studies: 4</t>
   </si>
 </sst>
 </file>
@@ -979,7 +1091,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="30.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="133.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1047,8 +1159,16 @@
         <v>14</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -1061,198 +1181,352 @@
   <cols>
     <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="23.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="17.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="12.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="33.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="110.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="14.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="55.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="64.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="100.71" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="125.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="33.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
         <v>22</v>
-      </c>
-      <c r="I1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2"/>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="n">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3"/>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4"/>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" t="s">
-        <v>50</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="23.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="21.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="21.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="29.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="17.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="13.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="33.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="139.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="15.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="14.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="15.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="69.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="64.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="56.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="125.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1320,1385 +1594,1501 @@
     <col min="61" max="61" width="14.71" hidden="0" customWidth="1"/>
     <col min="62" max="62" width="250.71" hidden="0" customWidth="1"/>
     <col min="63" max="63" width="64.71" hidden="0" customWidth="1"/>
-    <col min="64" max="64" width="15.71" hidden="0" customWidth="1"/>
-    <col min="65" max="65" width="25.71" hidden="0" customWidth="1"/>
+    <col min="64" max="64" width="23.71" hidden="0" customWidth="1"/>
+    <col min="65" max="65" width="21.71" hidden="0" customWidth="1"/>
+    <col min="66" max="66" width="20.71" hidden="0" customWidth="1"/>
+    <col min="67" max="67" width="21.71" hidden="0" customWidth="1"/>
+    <col min="68" max="68" width="19.71" hidden="0" customWidth="1"/>
+    <col min="69" max="69" width="18.71" hidden="0" customWidth="1"/>
+    <col min="70" max="70" width="10.71" hidden="0" customWidth="1"/>
+    <col min="71" max="71" width="151.71" hidden="0" customWidth="1"/>
+    <col min="72" max="72" width="13.71" hidden="0" customWidth="1"/>
+    <col min="73" max="73" width="30.71" hidden="0" customWidth="1"/>
+    <col min="74" max="74" width="15.71" hidden="0" customWidth="1"/>
+    <col min="75" max="75" width="23.71" hidden="0" customWidth="1"/>
+    <col min="76" max="76" width="21.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="J1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="L1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="N1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="O1" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="P1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="Q1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="R1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="S1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="T1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="U1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="V1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="W1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="X1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="Y1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="Z1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="AA1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AB1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AC1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE1" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="AF1" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AG1" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="AH1" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="AI1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ1" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK1" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="AL1" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="AM1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="AN1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="AP1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="AQ1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="AR1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="AS1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AT1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AU1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="AV1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="AW1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="AX1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AY1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="AZ1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="BA1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="BB1" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="BC1" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="BD1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="BE1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="BF1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="BG1" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="BH1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="BI1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="BJ1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="BK1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="BL1" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="BM1" t="s">
-        <v>109</v>
+        <v>125</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>130</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>132</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>133</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>43</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="F2" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="H2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="I2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="J2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="K2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="L2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="M2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="O2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="P2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Q2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="S2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="T2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="U2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="W2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Y2" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="Z2" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="AA2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AB2" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="AC2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AD2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="AF2" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AG2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="AH2" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="AI2" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AJ2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AK2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="AL2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="AM2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="AN2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AO2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AP2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AQ2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AR2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AS2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AT2" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="AU2" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="AV2" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="AW2" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="AX2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="AY2" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="AZ2" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="BA2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="BB2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="BC2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="BD2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="BE2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>47</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
       <c r="BI2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BJ2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BK2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>48</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="BL2"/>
       <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="F3" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="G3" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="I3" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="J3" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="K3" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="M3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="O3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="P3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Q3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="S3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="T3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="U3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="V3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="W3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="X3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Y3" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="Z3" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="AA3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AB3" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="AC3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AD3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="AF3" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AG3" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="AH3" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="AI3" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AK3" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="AL3" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="AM3" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="AN3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AO3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AP3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AQ3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AR3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AS3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AT3" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="AU3" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="AV3" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="AW3" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="AX3" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="AY3" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="AZ3" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="BA3" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="BB3" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="BC3" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="BD3" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="BE3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>47</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="BF3"/>
+      <c r="BG3"/>
+      <c r="BH3"/>
       <c r="BI3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BJ3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BK3" t="s">
-        <v>134</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>48</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="BL3"/>
       <c r="BM3"/>
+      <c r="BN3"/>
+      <c r="BO3"/>
+      <c r="BP3"/>
+      <c r="BQ3"/>
+      <c r="BR3"/>
+      <c r="BS3" t="s">
+        <v>166</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="F4" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="O4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="P4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Q4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="S4" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="T4" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="U4" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="V4" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="W4" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="X4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Y4" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="Z4" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="AA4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB4" t="s">
         <v>147</v>
       </c>
-      <c r="AB4" t="s">
-        <v>120</v>
-      </c>
       <c r="AC4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AD4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="AF4" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AG4" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="AH4" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="AI4" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="AJ4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AK4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AL4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AM4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AN4" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="AO4" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="AP4" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="AQ4" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="AR4" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="AS4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AT4" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="AU4" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="AV4" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="AW4" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="AX4" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="AY4" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="AZ4" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>47</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>47</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>47</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>47</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="BA4"/>
+      <c r="BB4"/>
+      <c r="BC4"/>
+      <c r="BD4"/>
       <c r="BE4" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="BF4" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="BG4" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="BH4" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="BI4" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="BJ4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BK4" t="s">
-        <v>145</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>41</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="BL4"/>
       <c r="BM4"/>
+      <c r="BN4"/>
+      <c r="BO4"/>
+      <c r="BP4"/>
+      <c r="BQ4"/>
+      <c r="BR4"/>
+      <c r="BS4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>179</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>58</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I5" t="s">
+        <v>185</v>
+      </c>
+      <c r="J5" t="s">
+        <v>186</v>
+      </c>
+      <c r="K5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L5" t="s">
+        <v>144</v>
+      </c>
+      <c r="M5" t="s">
+        <v>144</v>
+      </c>
+      <c r="N5" t="s">
+        <v>144</v>
+      </c>
+      <c r="O5" t="s">
+        <v>144</v>
+      </c>
+      <c r="P5" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>144</v>
+      </c>
+      <c r="R5" t="s">
+        <v>144</v>
+      </c>
+      <c r="S5" t="s">
+        <v>144</v>
+      </c>
+      <c r="T5" t="s">
+        <v>144</v>
+      </c>
+      <c r="U5" t="s">
+        <v>144</v>
+      </c>
+      <c r="V5" t="s">
+        <v>144</v>
+      </c>
+      <c r="W5" t="s">
+        <v>144</v>
+      </c>
+      <c r="X5" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>190</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE5" t="s">
         <v>148</v>
       </c>
-      <c r="B5" t="s">
+      <c r="AF5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>184</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>185</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>186</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>187</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>188</v>
+      </c>
+      <c r="AU5" t="s">
         <v>149</v>
       </c>
-      <c r="C5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="AV5" t="s">
         <v>150</v>
       </c>
-      <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="AW5" t="s">
         <v>151</v>
       </c>
-      <c r="I5" t="s">
-        <v>152</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="AX5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>183</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>184</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>185</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>186</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>187</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF5"/>
+      <c r="BG5"/>
+      <c r="BH5"/>
+      <c r="BI5" t="s">
+        <v>144</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>144</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>188</v>
+      </c>
+      <c r="BL5"/>
+      <c r="BM5"/>
+      <c r="BN5"/>
+      <c r="BO5"/>
+      <c r="BP5"/>
+      <c r="BQ5"/>
+      <c r="BR5"/>
+      <c r="BS5" t="s">
+        <v>191</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU5" t="s">
         <v>153</v>
       </c>
-      <c r="K5" t="s">
+      <c r="BV5" t="s">
         <v>154</v>
       </c>
-      <c r="L5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M5" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" t="s">
-        <v>47</v>
-      </c>
-      <c r="O5" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>47</v>
-      </c>
-      <c r="R5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U5" t="s">
-        <v>47</v>
-      </c>
-      <c r="V5" t="s">
-        <v>47</v>
-      </c>
-      <c r="W5" t="s">
-        <v>47</v>
-      </c>
-      <c r="X5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y5" t="s">
+      <c r="BW5" t="s">
         <v>155</v>
       </c>
-      <c r="Z5" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>150</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>151</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>154</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>123</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>124</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>125</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>150</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>46</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>151</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>152</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>153</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>154</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>47</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>47</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>47</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>47</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>155</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>48</v>
-      </c>
-      <c r="BM5"/>
+      <c r="BX5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="J6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="L6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="M6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="O6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="P6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Q6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="R6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="S6" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="T6" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="U6" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="V6" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="W6" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="X6" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="Y6" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="Z6" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="AA6" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="AB6" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="AC6" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="AD6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="AF6" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AG6" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="AH6" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="AI6" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="AJ6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AK6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AL6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AM6" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AN6" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="AO6" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="AP6" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="AQ6" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="AR6" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AS6" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="AT6" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="AU6" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="AV6" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="AW6" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="AX6" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="AY6" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="AZ6" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>47</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>47</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>47</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>47</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="BA6"/>
+      <c r="BB6"/>
+      <c r="BC6"/>
+      <c r="BD6"/>
       <c r="BE6" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="BF6" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="BG6" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="BH6" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="BI6" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="BJ6" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="BK6" t="s">
-        <v>166</v>
-      </c>
-      <c r="BL6" t="s">
-        <v>41</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="BL6"/>
       <c r="BM6"/>
+      <c r="BN6"/>
+      <c r="BO6"/>
+      <c r="BP6"/>
+      <c r="BQ6"/>
+      <c r="BR6"/>
+      <c r="BS6" t="s">
+        <v>204</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>30</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>179</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>58</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="B7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" t="s">
+        <v>144</v>
+      </c>
+      <c r="K7" t="s">
+        <v>144</v>
+      </c>
+      <c r="L7" t="s">
+        <v>144</v>
+      </c>
+      <c r="M7" t="s">
+        <v>144</v>
+      </c>
+      <c r="N7" t="s">
+        <v>144</v>
+      </c>
+      <c r="O7" t="s">
+        <v>144</v>
+      </c>
+      <c r="P7" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>144</v>
+      </c>
+      <c r="R7" t="s">
+        <v>144</v>
+      </c>
+      <c r="S7" t="s">
         <v>171</v>
       </c>
-      <c r="C7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>172</v>
-      </c>
-      <c r="F7" t="s">
-        <v>173</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K7" t="s">
-        <v>47</v>
-      </c>
-      <c r="L7" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" t="s">
-        <v>47</v>
-      </c>
-      <c r="O7" t="s">
-        <v>47</v>
-      </c>
-      <c r="P7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>47</v>
-      </c>
-      <c r="R7" t="s">
-        <v>47</v>
-      </c>
-      <c r="S7" t="s">
-        <v>140</v>
-      </c>
       <c r="T7" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="U7" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="V7" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="W7" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="X7" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="Y7" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="Z7" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>203</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>209</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>212</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>213</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>151</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>207</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>208</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA7"/>
+      <c r="BB7"/>
+      <c r="BC7"/>
+      <c r="BD7"/>
+      <c r="BE7" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>209</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>62</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>212</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>213</v>
+      </c>
+      <c r="BL7"/>
+      <c r="BM7"/>
+      <c r="BN7"/>
+      <c r="BO7"/>
+      <c r="BP7"/>
+      <c r="BQ7"/>
+      <c r="BR7"/>
+      <c r="BS7" t="s">
+        <v>215</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>30</v>
+      </c>
+      <c r="BU7" t="s">
         <v>179</v>
       </c>
-      <c r="AA7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>172</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>173</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>140</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>174</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>175</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>176</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>122</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>177</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>178</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>124</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>125</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>172</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>173</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>47</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>47</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>47</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>47</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>140</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>174</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>176</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>177</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>178</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>41</v>
-      </c>
-      <c r="BM7"/>
+      <c r="BV7" t="s">
+        <v>58</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BM7"/>
+  <autoFilter ref="A1:BX7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -2766,800 +3156,881 @@
     <col min="61" max="61" width="14.71" hidden="0" customWidth="1"/>
     <col min="62" max="62" width="26.71" hidden="0" customWidth="1"/>
     <col min="63" max="63" width="43.71" hidden="0" customWidth="1"/>
-    <col min="64" max="64" width="15.71" hidden="0" customWidth="1"/>
-    <col min="65" max="65" width="25.71" hidden="0" customWidth="1"/>
+    <col min="64" max="64" width="23.71" hidden="0" customWidth="1"/>
+    <col min="65" max="65" width="21.71" hidden="0" customWidth="1"/>
+    <col min="66" max="66" width="20.71" hidden="0" customWidth="1"/>
+    <col min="67" max="67" width="21.71" hidden="0" customWidth="1"/>
+    <col min="68" max="68" width="19.71" hidden="0" customWidth="1"/>
+    <col min="69" max="69" width="18.71" hidden="0" customWidth="1"/>
+    <col min="70" max="70" width="10.71" hidden="0" customWidth="1"/>
+    <col min="71" max="71" width="135.71" hidden="0" customWidth="1"/>
+    <col min="72" max="72" width="12.71" hidden="0" customWidth="1"/>
+    <col min="73" max="73" width="30.71" hidden="0" customWidth="1"/>
+    <col min="74" max="74" width="15.71" hidden="0" customWidth="1"/>
+    <col min="75" max="75" width="23.71" hidden="0" customWidth="1"/>
+    <col min="76" max="76" width="21.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="J1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="L1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="N1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="O1" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="P1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="Q1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="R1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="S1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="T1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="U1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="V1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="W1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="X1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="Y1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="Z1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="AA1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AB1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AC1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE1" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="AF1" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AG1" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="AH1" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="AI1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ1" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK1" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="AL1" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="AM1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="AN1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="AP1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="AQ1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="AR1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="AS1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AT1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AU1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="AV1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="AW1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="AX1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AY1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="AZ1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="BA1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="BB1" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="BC1" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="BD1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="BE1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="BF1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="BG1" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="BH1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="BI1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="BJ1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="BK1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="BL1" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="BM1" t="s">
-        <v>109</v>
+        <v>125</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>130</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>132</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>133</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>43</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="F2" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="G2" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="H2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="I2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="J2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="K2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="L2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="M2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="O2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="P2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Q2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="S2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="T2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="U2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="W2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Y2" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="Z2" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="AA2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AB2" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="AC2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AD2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="AF2" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AG2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="AH2" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="AI2" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AJ2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="AK2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="AL2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="AM2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="AN2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AO2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AP2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AQ2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AR2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AS2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AT2" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="AU2" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="AV2" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="AW2" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="AX2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="AY2" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="AZ2" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="BA2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="BB2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="BC2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="BD2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="BE2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>47</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
       <c r="BI2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BJ2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BK2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>48</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="BL2"/>
       <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="F3" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="G3" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="H3" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="I3" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="J3" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="K3" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="M3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="O3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="P3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Q3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="S3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="T3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="U3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="V3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="W3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="X3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Y3" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="Z3" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="AA3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AB3" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="AC3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AD3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="AF3" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AG3" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="AH3" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="AI3" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="AJ3" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AK3" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="AL3" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="AM3" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="AN3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AO3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AP3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AQ3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AR3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AS3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AT3" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="AU3" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="AV3" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="AW3" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="AX3" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="AY3" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="AZ3" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="BA3" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="BB3" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="BC3" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="BD3" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="BE3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>47</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="BF3"/>
+      <c r="BG3"/>
+      <c r="BH3"/>
       <c r="BI3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BJ3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BK3" t="s">
-        <v>134</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>48</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="BL3"/>
       <c r="BM3"/>
+      <c r="BN3"/>
+      <c r="BO3"/>
+      <c r="BP3"/>
+      <c r="BQ3"/>
+      <c r="BR3"/>
+      <c r="BS3" t="s">
+        <v>166</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="F4" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="O4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="P4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Q4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="S4" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="T4" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="U4" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="V4" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="W4" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="X4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Y4" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="Z4" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="AA4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB4" t="s">
         <v>147</v>
       </c>
-      <c r="AB4" t="s">
-        <v>120</v>
-      </c>
       <c r="AC4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AD4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="AF4" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AG4" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="AH4" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="AI4" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="AJ4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AK4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AL4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AM4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AN4" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="AO4" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="AP4" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="AQ4" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="AR4" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="AS4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AT4" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="AU4" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="AV4" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="AW4" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="AX4" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="AY4" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="AZ4" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>47</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>47</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>47</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>47</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="BA4"/>
+      <c r="BB4"/>
+      <c r="BC4"/>
+      <c r="BD4"/>
       <c r="BE4" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="BF4" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="BG4" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="BH4" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="BI4" t="s">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="BJ4" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="BK4" t="s">
-        <v>145</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>41</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="BL4"/>
       <c r="BM4"/>
+      <c r="BN4"/>
+      <c r="BO4"/>
+      <c r="BP4"/>
+      <c r="BQ4"/>
+      <c r="BR4"/>
+      <c r="BS4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>179</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>58</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BM4"/>
+  <autoFilter ref="A1:BX4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -3627,605 +4098,671 @@
     <col min="61" max="61" width="14.71" hidden="0" customWidth="1"/>
     <col min="62" max="62" width="250.71" hidden="0" customWidth="1"/>
     <col min="63" max="63" width="29.71" hidden="0" customWidth="1"/>
-    <col min="64" max="64" width="15.71" hidden="0" customWidth="1"/>
-    <col min="65" max="65" width="25.71" hidden="0" customWidth="1"/>
+    <col min="64" max="64" width="23.71" hidden="0" customWidth="1"/>
+    <col min="65" max="65" width="21.71" hidden="0" customWidth="1"/>
+    <col min="66" max="66" width="20.71" hidden="0" customWidth="1"/>
+    <col min="67" max="67" width="21.71" hidden="0" customWidth="1"/>
+    <col min="68" max="68" width="19.71" hidden="0" customWidth="1"/>
+    <col min="69" max="69" width="18.71" hidden="0" customWidth="1"/>
+    <col min="70" max="70" width="10.71" hidden="0" customWidth="1"/>
+    <col min="71" max="71" width="89.71" hidden="0" customWidth="1"/>
+    <col min="72" max="72" width="13.71" hidden="0" customWidth="1"/>
+    <col min="73" max="73" width="21.71" hidden="0" customWidth="1"/>
+    <col min="74" max="74" width="15.71" hidden="0" customWidth="1"/>
+    <col min="75" max="75" width="23.71" hidden="0" customWidth="1"/>
+    <col min="76" max="76" width="21.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="J1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="L1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="N1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="O1" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="P1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="Q1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="R1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="S1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="T1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="U1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="V1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="W1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="X1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="Y1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="Z1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="AA1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AB1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AC1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE1" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="AF1" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AG1" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="AH1" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="AI1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ1" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK1" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="AL1" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="AM1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="AN1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="AP1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="AQ1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="AR1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="AS1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AT1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AU1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="AV1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="AW1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="AX1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AY1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="AZ1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="BA1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="BB1" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="BC1" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="BD1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="BE1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="BF1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="BG1" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="BH1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="BI1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="BJ1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="BK1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="BL1" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="BM1" t="s">
-        <v>109</v>
+        <v>125</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>130</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>132</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>133</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>43</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="H2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="I2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="J2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="K2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="L2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="M2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="O2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="P2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="Q2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="S2" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="T2" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="U2" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="V2" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="W2" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="X2" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="Y2" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="Z2" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="AA2" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="AB2" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="AC2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="AD2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="AF2" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AG2" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="AH2" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="AI2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="AJ2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AK2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AL2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AM2" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="AN2" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="AO2" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="AP2" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="AQ2" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="AR2" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="AS2" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="AT2" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="AU2" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="AV2" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="AW2" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="AX2" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="AY2" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="AZ2" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>47</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
       <c r="BE2" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="BF2" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="BG2" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="BH2" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="BI2" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="BJ2" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="BK2" t="s">
-        <v>166</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>41</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="BL2"/>
       <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2" t="s">
+        <v>204</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>30</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>179</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>58</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M3" t="s">
+        <v>144</v>
+      </c>
+      <c r="N3" t="s">
+        <v>144</v>
+      </c>
+      <c r="O3" t="s">
+        <v>144</v>
+      </c>
+      <c r="P3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R3" t="s">
+        <v>144</v>
+      </c>
+      <c r="S3" t="s">
         <v>171</v>
       </c>
-      <c r="C3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>47</v>
-      </c>
-      <c r="R3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S3" t="s">
-        <v>140</v>
-      </c>
       <c r="T3" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="U3" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="V3" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="W3" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="X3" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="Y3" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="Z3" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>203</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>209</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>210</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>212</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>213</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>207</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>208</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA3"/>
+      <c r="BB3"/>
+      <c r="BC3"/>
+      <c r="BD3"/>
+      <c r="BE3" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>209</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>62</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>212</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>213</v>
+      </c>
+      <c r="BL3"/>
+      <c r="BM3"/>
+      <c r="BN3"/>
+      <c r="BO3"/>
+      <c r="BP3"/>
+      <c r="BQ3"/>
+      <c r="BR3"/>
+      <c r="BS3" t="s">
+        <v>215</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>30</v>
+      </c>
+      <c r="BU3" t="s">
         <v>179</v>
       </c>
-      <c r="AA3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>172</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>173</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>174</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>175</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>176</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>177</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>178</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>123</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>124</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>125</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>172</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>173</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>41</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>140</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>174</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>175</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>176</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>122</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>177</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>178</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>41</v>
-      </c>
-      <c r="BM3"/>
+      <c r="BV3" t="s">
+        <v>58</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BM3"/>
+  <autoFilter ref="A1:BX3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -4234,9 +4771,9 @@
     <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="16.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="33.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="113.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="27.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="183.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="51.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="19.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="18.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="17.71" hidden="0" customWidth="1"/>
@@ -4255,15 +4792,15 @@
     <col min="23" max="23" width="8.71" hidden="0" customWidth="1"/>
     <col min="24" max="24" width="20.71" hidden="0" customWidth="1"/>
     <col min="25" max="25" width="64.71" hidden="0" customWidth="1"/>
-    <col min="26" max="26" width="115.71" hidden="0" customWidth="1"/>
-    <col min="27" max="27" width="16.71" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="137.71" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="59.71" hidden="0" customWidth="1"/>
     <col min="28" max="28" width="17.71" hidden="0" customWidth="1"/>
     <col min="29" max="29" width="18.71" hidden="0" customWidth="1"/>
     <col min="30" max="30" width="15.71" hidden="0" customWidth="1"/>
     <col min="31" max="31" width="19.71" hidden="0" customWidth="1"/>
     <col min="32" max="32" width="33.71" hidden="0" customWidth="1"/>
-    <col min="33" max="33" width="113.71" hidden="0" customWidth="1"/>
-    <col min="34" max="34" width="27.71" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="183.71" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="51.71" hidden="0" customWidth="1"/>
     <col min="35" max="35" width="24.71" hidden="0" customWidth="1"/>
     <col min="36" max="36" width="34.71" hidden="0" customWidth="1"/>
     <col min="37" max="37" width="33.71" hidden="0" customWidth="1"/>
@@ -4279,8 +4816,8 @@
     <col min="47" max="47" width="75.71" hidden="0" customWidth="1"/>
     <col min="48" max="48" width="10.71" hidden="0" customWidth="1"/>
     <col min="49" max="49" width="19.71" hidden="0" customWidth="1"/>
-    <col min="50" max="50" width="113.71" hidden="0" customWidth="1"/>
-    <col min="51" max="51" width="27.71" hidden="0" customWidth="1"/>
+    <col min="50" max="50" width="183.71" hidden="0" customWidth="1"/>
+    <col min="51" max="51" width="51.71" hidden="0" customWidth="1"/>
     <col min="52" max="52" width="15.71" hidden="0" customWidth="1"/>
     <col min="53" max="53" width="25.71" hidden="0" customWidth="1"/>
     <col min="54" max="54" width="24.71" hidden="0" customWidth="1"/>
@@ -4293,410 +4830,1089 @@
     <col min="61" max="61" width="14.71" hidden="0" customWidth="1"/>
     <col min="62" max="62" width="26.71" hidden="0" customWidth="1"/>
     <col min="63" max="63" width="64.71" hidden="0" customWidth="1"/>
-    <col min="64" max="64" width="15.71" hidden="0" customWidth="1"/>
-    <col min="65" max="65" width="25.71" hidden="0" customWidth="1"/>
+    <col min="64" max="64" width="23.71" hidden="0" customWidth="1"/>
+    <col min="65" max="65" width="21.71" hidden="0" customWidth="1"/>
+    <col min="66" max="66" width="20.71" hidden="0" customWidth="1"/>
+    <col min="67" max="67" width="21.71" hidden="0" customWidth="1"/>
+    <col min="68" max="68" width="19.71" hidden="0" customWidth="1"/>
+    <col min="69" max="69" width="18.71" hidden="0" customWidth="1"/>
+    <col min="70" max="70" width="10.71" hidden="0" customWidth="1"/>
+    <col min="71" max="71" width="151.71" hidden="0" customWidth="1"/>
+    <col min="72" max="72" width="12.71" hidden="0" customWidth="1"/>
+    <col min="73" max="73" width="30.71" hidden="0" customWidth="1"/>
+    <col min="74" max="74" width="15.71" hidden="0" customWidth="1"/>
+    <col min="75" max="75" width="23.71" hidden="0" customWidth="1"/>
+    <col min="76" max="76" width="21.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="J1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="L1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="N1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="O1" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="P1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="Q1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="R1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="S1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="T1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="U1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="V1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="W1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="X1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="Y1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="Z1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="AA1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AB1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AC1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE1" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="AF1" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AG1" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="AH1" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="AI1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ1" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK1" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="AL1" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="AM1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="AN1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="AP1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="AQ1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="AR1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="AS1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AT1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="AU1" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="AV1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="AW1" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="AX1" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AY1" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="AZ1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="BA1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="BB1" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="BC1" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="BD1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="BE1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="BF1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="BG1" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="BH1" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="BI1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="BJ1" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="BK1" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="BL1" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="BM1" t="s">
-        <v>109</v>
+        <v>125</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>130</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>131</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>132</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>133</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>43</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M2" t="s">
+        <v>144</v>
+      </c>
+      <c r="N2" t="s">
+        <v>144</v>
+      </c>
+      <c r="O2" t="s">
+        <v>144</v>
+      </c>
+      <c r="P2" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>144</v>
+      </c>
+      <c r="R2" t="s">
+        <v>144</v>
+      </c>
+      <c r="S2" t="s">
+        <v>144</v>
+      </c>
+      <c r="T2" t="s">
+        <v>144</v>
+      </c>
+      <c r="U2" t="s">
+        <v>144</v>
+      </c>
+      <c r="V2" t="s">
+        <v>144</v>
+      </c>
+      <c r="W2" t="s">
+        <v>144</v>
+      </c>
+      <c r="X2" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE2" t="s">
         <v>148</v>
       </c>
-      <c r="B2" t="s">
+      <c r="AF2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AU2" t="s">
         <v>149</v>
       </c>
-      <c r="C2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="AV2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>142</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>144</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2" t="s">
+        <v>152</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>154</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K3" t="s">
+        <v>163</v>
+      </c>
+      <c r="L3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M3" t="s">
+        <v>144</v>
+      </c>
+      <c r="N3" t="s">
+        <v>144</v>
+      </c>
+      <c r="O3" t="s">
+        <v>144</v>
+      </c>
+      <c r="P3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>144</v>
+      </c>
+      <c r="R3" t="s">
+        <v>144</v>
+      </c>
+      <c r="S3" t="s">
+        <v>144</v>
+      </c>
+      <c r="T3" t="s">
+        <v>144</v>
+      </c>
+      <c r="U3" t="s">
+        <v>144</v>
+      </c>
+      <c r="V3" t="s">
+        <v>144</v>
+      </c>
+      <c r="W3" t="s">
+        <v>144</v>
+      </c>
+      <c r="X3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>147</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>162</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>164</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>151</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>158</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>161</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>162</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>163</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF3"/>
+      <c r="BG3"/>
+      <c r="BH3"/>
+      <c r="BI3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>164</v>
+      </c>
+      <c r="BL3"/>
+      <c r="BM3"/>
+      <c r="BN3"/>
+      <c r="BO3"/>
+      <c r="BP3"/>
+      <c r="BQ3"/>
+      <c r="BR3"/>
+      <c r="BS3" t="s">
+        <v>166</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I4" t="s">
+        <v>144</v>
+      </c>
+      <c r="J4" t="s">
+        <v>144</v>
+      </c>
+      <c r="K4" t="s">
+        <v>144</v>
+      </c>
+      <c r="L4" t="s">
+        <v>144</v>
+      </c>
+      <c r="M4" t="s">
+        <v>144</v>
+      </c>
+      <c r="N4" t="s">
+        <v>144</v>
+      </c>
+      <c r="O4" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>144</v>
+      </c>
+      <c r="R4" t="s">
+        <v>144</v>
+      </c>
+      <c r="S4" t="s">
+        <v>171</v>
+      </c>
+      <c r="T4" t="s">
+        <v>172</v>
+      </c>
+      <c r="U4" t="s">
+        <v>173</v>
+      </c>
+      <c r="V4" t="s">
+        <v>174</v>
+      </c>
+      <c r="W4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X4" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>172</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>173</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>174</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>175</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>169</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>58</v>
+      </c>
+      <c r="BA4"/>
+      <c r="BB4"/>
+      <c r="BC4"/>
+      <c r="BD4"/>
+      <c r="BE4" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>172</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>173</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>174</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>49</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>144</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>175</v>
+      </c>
+      <c r="BL4"/>
+      <c r="BM4"/>
+      <c r="BN4"/>
+      <c r="BO4"/>
+      <c r="BP4"/>
+      <c r="BQ4"/>
+      <c r="BR4"/>
+      <c r="BS4" t="s">
+        <v>178</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>179</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>58</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BX4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I5" t="s">
+        <v>185</v>
+      </c>
+      <c r="J5" t="s">
+        <v>186</v>
+      </c>
+      <c r="K5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L5" t="s">
+        <v>144</v>
+      </c>
+      <c r="M5" t="s">
+        <v>144</v>
+      </c>
+      <c r="N5" t="s">
+        <v>144</v>
+      </c>
+      <c r="O5" t="s">
+        <v>144</v>
+      </c>
+      <c r="P5" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>144</v>
+      </c>
+      <c r="R5" t="s">
+        <v>144</v>
+      </c>
+      <c r="S5" t="s">
+        <v>144</v>
+      </c>
+      <c r="T5" t="s">
+        <v>144</v>
+      </c>
+      <c r="U5" t="s">
+        <v>144</v>
+      </c>
+      <c r="V5" t="s">
+        <v>144</v>
+      </c>
+      <c r="W5" t="s">
+        <v>144</v>
+      </c>
+      <c r="X5" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>190</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" t="s">
         <v>31</v>
       </c>
-      <c r="E2" t="s">
+      <c r="AE5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>184</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>185</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>186</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>187</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>188</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV5" t="s">
         <v>150</v>
       </c>
-      <c r="F2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="AW5" t="s">
         <v>151</v>
       </c>
-      <c r="I2" t="s">
-        <v>152</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="AX5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>183</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>184</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>185</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>186</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>187</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>52</v>
+      </c>
+      <c r="BF5"/>
+      <c r="BG5"/>
+      <c r="BH5"/>
+      <c r="BI5" t="s">
+        <v>144</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>144</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>188</v>
+      </c>
+      <c r="BL5"/>
+      <c r="BM5"/>
+      <c r="BN5"/>
+      <c r="BO5"/>
+      <c r="BP5"/>
+      <c r="BQ5"/>
+      <c r="BR5"/>
+      <c r="BS5" t="s">
+        <v>191</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>26</v>
+      </c>
+      <c r="BU5" t="s">
         <v>153</v>
       </c>
-      <c r="K2" t="s">
+      <c r="BV5" t="s">
         <v>154</v>
       </c>
-      <c r="L2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N2" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" t="s">
-        <v>47</v>
-      </c>
-      <c r="P2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>47</v>
-      </c>
-      <c r="R2" t="s">
-        <v>47</v>
-      </c>
-      <c r="S2" t="s">
-        <v>47</v>
-      </c>
-      <c r="T2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="BW5" t="s">
         <v>155</v>
       </c>
-      <c r="Z2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>152</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>46</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>154</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>47</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>155</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>48</v>
-      </c>
-      <c r="BM2"/>
+      <c r="BX5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BM2"/>
+  <autoFilter ref="A1:BX5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -4706,217 +5922,217 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>189</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>198</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>203</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>206</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
